--- a/InputData/land/CApULAbIFM/CO2 Abated per Unit Land Area by Impr For Mgmt.xlsx
+++ b/InputData/land/CApULAbIFM/CO2 Abated per Unit Land Area by Impr For Mgmt.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10509"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28619"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anaxolt/Google Drive/2021/D.Development/TARGET_eps-us-3.2.1/InputData/land/CApULAbIFM/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/skorpius/My Drive/2024/FO local_EPS ICM/Diario/20250226_CATCHUP/land_CPL/CApULAbIFM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6B4D18D-25EE-D943-8D53-233DD4980015}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7184B9D8-C2A5-A142-81BA-C3E26AF66944}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="320" yWindow="500" windowWidth="21080" windowHeight="16200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="9620" yWindow="-21100" windowWidth="33340" windowHeight="20700" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -18,8 +18,11 @@
     <sheet name="Calculations" sheetId="4" r:id="rId3"/>
     <sheet name="CApULAbIFM" sheetId="3" r:id="rId4"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191028"/>
   <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -27,6 +30,8 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -34,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="36">
   <si>
     <t>CApULAbIFM CO2 Abated per Unit Land Area by Improved Forest Management</t>
   </si>
@@ -42,89 +47,113 @@
     <t>Source:</t>
   </si>
   <si>
+    <t>Instituto Nacional de Ecología y Cambio Climático (INECC)</t>
+  </si>
+  <si>
+    <t>1997 (estimates for 2000,2010,2030)</t>
+  </si>
+  <si>
+    <t>Carbon emissions capture in Mexico</t>
+  </si>
+  <si>
+    <t>Cuadro 3.4</t>
+  </si>
+  <si>
+    <t>Note</t>
+  </si>
+  <si>
+    <t>Estimation based on Masera,Ordoñez,1997 study.</t>
+  </si>
+  <si>
+    <t>No newer studies available</t>
+  </si>
+  <si>
+    <t>The study defines the carbon capture potential for a forested area,</t>
+  </si>
+  <si>
+    <t>yet it does not establish a value per year or for how long a period.</t>
+  </si>
+  <si>
+    <t>A 30 year period was assumed.</t>
+  </si>
+  <si>
+    <t>It returns a value 2.5e6 compared to US value of 1.5e6</t>
+  </si>
+  <si>
+    <t>This could be calibrated by adjusting the period.</t>
+  </si>
+  <si>
+    <t>Technical potential</t>
+  </si>
+  <si>
+    <t>Area (million hectares)</t>
+  </si>
+  <si>
+    <t>Accumulated CO2 (Gton)</t>
+  </si>
+  <si>
+    <t>Translation</t>
+  </si>
+  <si>
+    <t>Forestry policy</t>
+  </si>
+  <si>
+    <t>Improved forest mgmt</t>
+  </si>
+  <si>
+    <t>Manejo forestal</t>
+  </si>
+  <si>
+    <t>Sistemas agroforestales</t>
+  </si>
+  <si>
+    <t>Conversion factors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 G = </t>
+  </si>
+  <si>
+    <t>1 ton =</t>
+  </si>
+  <si>
+    <t>kg</t>
+  </si>
+  <si>
+    <t>1 kg =</t>
+  </si>
+  <si>
+    <t>g</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Potential </t>
+  </si>
+  <si>
+    <t>Area (acres)</t>
+  </si>
+  <si>
+    <t>Accumulated CO2 (g)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 ha = </t>
+  </si>
+  <si>
+    <t>acres</t>
+  </si>
+  <si>
+    <t>Se consideran 30 años de acumulación</t>
+  </si>
+  <si>
+    <t>Per Acre</t>
+  </si>
+  <si>
     <t>CO2 Abated (g)</t>
-  </si>
-  <si>
-    <t>Per Acre</t>
-  </si>
-  <si>
-    <t>Instituto Nacional de Ecología y Cambio Climático (INECC)</t>
-  </si>
-  <si>
-    <t>1997 (estimates for 2000,2010,2030)</t>
-  </si>
-  <si>
-    <t>Carbon emissions capture in Mexico</t>
-  </si>
-  <si>
-    <t>https://www.fas.org/sgp/crs/misc/R40562.pdf</t>
-  </si>
-  <si>
-    <t>Cuadro 3.4</t>
-  </si>
-  <si>
-    <t>Technical potential</t>
-  </si>
-  <si>
-    <t>Area (million hectares)</t>
-  </si>
-  <si>
-    <t>Accumulated CO2 (Gton)</t>
-  </si>
-  <si>
-    <t>Translation</t>
-  </si>
-  <si>
-    <t>Forestry policy</t>
-  </si>
-  <si>
-    <t>Improved forest mgmt</t>
-  </si>
-  <si>
-    <t>Manejo forestal</t>
-  </si>
-  <si>
-    <t>Sistemas agroforestales</t>
-  </si>
-  <si>
-    <t>Conversion factors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 G = </t>
-  </si>
-  <si>
-    <t>1 ton =</t>
-  </si>
-  <si>
-    <t>kg</t>
-  </si>
-  <si>
-    <t>1 kg =</t>
-  </si>
-  <si>
-    <t>g</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Potential </t>
-  </si>
-  <si>
-    <t>Area (acres)</t>
-  </si>
-  <si>
-    <t>Accumulated CO2 (g)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1 ha = </t>
-  </si>
-  <si>
-    <t>acres</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -141,15 +170,14 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -159,6 +187,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -213,11 +247,10 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -227,29 +260,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -257,25 +274,41 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -353,9 +386,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -393,9 +426,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -428,26 +461,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -480,26 +496,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -673,53 +672,84 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:B15"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" s="1"/>
       <c r="B4" s="4" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5" s="1"/>
       <c r="B5" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="1"/>
+      <c r="B6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="1"/>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="1" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A6" s="1"/>
-      <c r="B6" s="5" t="s">
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A7" s="1"/>
-      <c r="B7" t="s">
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
-      <c r="A9" s="1"/>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" t="s">
+        <v>13</v>
+      </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B6" r:id="rId1" xr:uid="{0AA3972E-175E-184B-8289-F7FC2C975BBA}"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -727,183 +757,181 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63C3D21A-600C-324F-968E-57E19A5EC2D8}">
   <dimension ref="B33:J43"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15"/>
   <sheetData>
-    <row r="33" spans="2:10" ht="48" x14ac:dyDescent="0.2">
-      <c r="B33" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C33" s="7"/>
-      <c r="D33" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E33" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F33" s="9"/>
-    </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B34" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C34" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="D34" s="11">
+    <row r="33" spans="2:10" ht="48">
+      <c r="B33" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C33" s="19"/>
+      <c r="D33" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E33" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="F33" s="20"/>
+    </row>
+    <row r="34" spans="2:10">
+      <c r="B34" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D34" s="7">
         <v>2030</v>
       </c>
-      <c r="E34" s="12">
+      <c r="E34" s="16">
         <v>2030</v>
       </c>
-      <c r="F34" s="13"/>
-    </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B35" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C35" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="D35" s="15">
+      <c r="F34" s="17"/>
+    </row>
+    <row r="35" spans="2:10">
+      <c r="B35" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D35" s="9">
         <v>18.7</v>
       </c>
-      <c r="E35" s="14">
+      <c r="E35" s="8">
         <v>2.13</v>
       </c>
-      <c r="F35" s="14">
+      <c r="F35" s="8">
         <v>2.8</v>
       </c>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B36" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C36" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="D36" s="16">
+    <row r="36" spans="2:10">
+      <c r="B36" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C36" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D36" s="10">
         <v>1.9</v>
       </c>
-      <c r="E36" s="17">
+      <c r="E36" s="23">
         <v>0.1</v>
       </c>
-      <c r="F36" s="18"/>
-      <c r="H36" s="12" t="s">
+      <c r="F36" s="22"/>
+      <c r="H36" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="I36" s="17"/>
+    </row>
+    <row r="37" spans="2:10">
+      <c r="D37" s="11"/>
+      <c r="E37" s="11"/>
+      <c r="F37" s="11"/>
+      <c r="H37" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="I37" s="12">
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10">
+      <c r="H38" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I38" s="8">
+        <v>1000</v>
+      </c>
+      <c r="J38" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="39" spans="2:10">
+      <c r="H39" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="I39" s="8">
+        <v>1000</v>
+      </c>
+      <c r="J39" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="40" spans="2:10" ht="15.95">
+      <c r="B40" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="C40" s="19"/>
+      <c r="D40" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E40" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="F40" s="20"/>
+      <c r="H40" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="I40" s="8">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="J40" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="41" spans="2:10">
+      <c r="B41" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="I36" s="13"/>
-    </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="D37" s="19"/>
-      <c r="E37" s="19"/>
-      <c r="F37" s="19"/>
-      <c r="H37" s="15" t="s">
+      <c r="C41" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="I37" s="20">
-        <v>1000000000</v>
-      </c>
-    </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H38" s="14" t="s">
+      <c r="D41" s="7">
+        <v>2030</v>
+      </c>
+      <c r="E41" s="16">
+        <v>2030</v>
+      </c>
+      <c r="F41" s="17"/>
+    </row>
+    <row r="42" spans="2:10">
+      <c r="B42" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="I38" s="14">
-        <v>1000</v>
-      </c>
-      <c r="J38" t="s">
+      <c r="C42" s="8" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H39" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="I39" s="14">
-        <v>1000</v>
-      </c>
-      <c r="J39" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="40" spans="2:10" ht="16" x14ac:dyDescent="0.2">
-      <c r="B40" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C40" s="7"/>
-      <c r="D40" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E40" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="F40" s="9"/>
-      <c r="H40" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="I40" s="14">
-        <v>2.4700000000000002</v>
-      </c>
-      <c r="J40" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B41" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C41" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="D41" s="11">
-        <v>2030</v>
-      </c>
-      <c r="E41" s="12">
-        <v>2030</v>
-      </c>
-      <c r="F41" s="13"/>
-    </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B42" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C42" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="D42" s="15">
+      <c r="D42" s="9">
         <f>D35*I40*1000000</f>
         <v>46189000</v>
       </c>
-      <c r="E42" s="21">
+      <c r="E42" s="13">
         <f>E35*I38*I39*I37</f>
         <v>2130000000000000</v>
       </c>
-      <c r="F42" s="21">
+      <c r="F42" s="13">
         <f>F35*I38*I39*I37</f>
         <v>2800000000000000</v>
       </c>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B43" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C43" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="D43" s="16">
+    <row r="43" spans="2:10">
+      <c r="B43" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C43" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D43" s="10">
         <f>D36*I40*1000000</f>
         <v>4693000.0000000009</v>
       </c>
-      <c r="E43" s="22">
+      <c r="E43" s="21">
         <f>E36*I38*I39*I37</f>
         <v>100000000000000</v>
       </c>
-      <c r="F43" s="18"/>
+      <c r="F43" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="E41:F41"/>
-    <mergeCell ref="E43:F43"/>
     <mergeCell ref="B33:C33"/>
     <mergeCell ref="E33:F33"/>
     <mergeCell ref="E34:F34"/>
@@ -911,6 +939,8 @@
     <mergeCell ref="H36:I36"/>
     <mergeCell ref="B40:C40"/>
     <mergeCell ref="E40:F40"/>
+    <mergeCell ref="E41:F41"/>
+    <mergeCell ref="E43:F43"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
@@ -919,187 +949,199 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B3:J13"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <dimension ref="B3:J17"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="19" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:10" ht="48" x14ac:dyDescent="0.2">
-      <c r="B3" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="7"/>
-      <c r="D3" s="8" t="s">
-        <v>10</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="F3" s="9"/>
-    </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B4" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="11">
+    <row r="3" spans="2:10" ht="48">
+      <c r="B3" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" s="19"/>
+      <c r="D3" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="E3" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="F3" s="20"/>
+    </row>
+    <row r="4" spans="2:10">
+      <c r="B4" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="D4" s="7">
         <v>2030</v>
       </c>
-      <c r="E4" s="12">
+      <c r="E4" s="16">
         <v>2030</v>
       </c>
-      <c r="F4" s="13"/>
-    </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B5" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" s="15">
+      <c r="F4" s="17"/>
+    </row>
+    <row r="5" spans="2:10">
+      <c r="B5" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="9">
         <v>18.7</v>
       </c>
-      <c r="E5" s="14">
+      <c r="E5" s="8">
         <v>2.13</v>
       </c>
-      <c r="F5" s="14">
+      <c r="F5" s="8">
         <v>2.8</v>
       </c>
     </row>
-    <row r="6" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B6" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="16">
+    <row r="6" spans="2:10">
+      <c r="B6" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6" s="10">
         <v>1.9</v>
       </c>
-      <c r="E6" s="17">
+      <c r="E6" s="23">
         <v>0.1</v>
       </c>
-      <c r="F6" s="18"/>
-      <c r="H6" s="12" t="s">
+      <c r="F6" s="22"/>
+      <c r="H6" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="I6" s="17"/>
+    </row>
+    <row r="7" spans="2:10">
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="11"/>
+      <c r="H7" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="I7" s="12">
+        <v>1000000000</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10">
+      <c r="H8" s="8" t="s">
+        <v>24</v>
+      </c>
+      <c r="I8" s="8">
+        <v>1000</v>
+      </c>
+      <c r="J8" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10">
+      <c r="H9" s="8" t="s">
+        <v>26</v>
+      </c>
+      <c r="I9" s="8">
+        <v>1000</v>
+      </c>
+      <c r="J9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10" ht="32.1">
+      <c r="B10" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="C10" s="19"/>
+      <c r="D10" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>30</v>
+      </c>
+      <c r="F10" s="20"/>
+      <c r="H10" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="I10" s="8">
+        <v>2.4700000000000002</v>
+      </c>
+      <c r="J10" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10">
+      <c r="B11" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="I6" s="13"/>
-    </row>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="D7" s="19"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="19"/>
-      <c r="H7" s="15" t="s">
+      <c r="C11" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="I7" s="20">
-        <v>1000000000</v>
-      </c>
-    </row>
-    <row r="8" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H8" s="14" t="s">
+      <c r="D11" s="7">
+        <v>2030</v>
+      </c>
+      <c r="E11" s="16">
+        <v>2030</v>
+      </c>
+      <c r="F11" s="17"/>
+    </row>
+    <row r="12" spans="2:10">
+      <c r="B12" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="I8" s="14">
-        <v>1000</v>
-      </c>
-      <c r="J8" t="s">
+      <c r="C12" s="8" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="H9" s="14" t="s">
-        <v>21</v>
-      </c>
-      <c r="I9" s="14">
-        <v>1000</v>
-      </c>
-      <c r="J9" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="2:10" ht="32" x14ac:dyDescent="0.2">
-      <c r="B10" s="6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C10" s="7"/>
-      <c r="D10" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="E10" s="9" t="s">
-        <v>25</v>
-      </c>
-      <c r="F10" s="9"/>
-      <c r="H10" s="14" t="s">
-        <v>26</v>
-      </c>
-      <c r="I10" s="14">
-        <v>2.4700000000000002</v>
-      </c>
-      <c r="J10" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B11" s="10" t="s">
-        <v>12</v>
-      </c>
-      <c r="C11" s="10" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" s="11">
-        <v>2030</v>
-      </c>
-      <c r="E11" s="12">
-        <v>2030</v>
-      </c>
-      <c r="F11" s="13"/>
-    </row>
-    <row r="12" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B12" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C12" s="14" t="s">
-        <v>15</v>
-      </c>
-      <c r="D12" s="15">
+      <c r="D12" s="9">
         <f>D5*I10*1000000</f>
         <v>46189000</v>
       </c>
-      <c r="E12" s="21">
+      <c r="E12" s="13">
         <f>E5*I8*I9*I7</f>
         <v>2130000000000000</v>
       </c>
-      <c r="F12" s="21">
+      <c r="F12" s="13">
         <f>F5*I8*I9*I7</f>
         <v>2800000000000000</v>
       </c>
     </row>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.2">
-      <c r="B13" s="14" t="s">
-        <v>14</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" s="16">
+    <row r="13" spans="2:10">
+      <c r="B13" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="C13" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="D13" s="10">
         <f>D6*I10*1000000</f>
         <v>4693000.0000000009</v>
       </c>
-      <c r="E13" s="22">
+      <c r="E13" s="21">
         <f>E6*I8*I9*I7</f>
         <v>100000000000000</v>
       </c>
-      <c r="F13" s="18"/>
+      <c r="F13" s="22"/>
+    </row>
+    <row r="15" spans="2:10">
+      <c r="B15" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="E15" s="15">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="17" spans="5:5">
+      <c r="E17" s="3">
+        <f>((AVERAGE(Calculations!E12:F12)/Calculations!D12)+(Calculations!E13/Calculations!D13))/E15</f>
+        <v>2489200.5501423785</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="E13:F13"/>
     <mergeCell ref="B3:C3"/>
     <mergeCell ref="E3:F3"/>
     <mergeCell ref="E4:F4"/>
@@ -1107,6 +1149,8 @@
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="B10:C10"/>
     <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E13:F13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1118,26 +1162,197 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="15.1640625" customWidth="1"/>
+    <col min="1" max="1" width="15.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2">
       <c r="B1" s="2" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.2">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="B2" s="3">
-        <f>((AVERAGE(Calculations!E12:F12)/Calculations!D12)+(Calculations!E13/Calculations!D13))/30</f>
+        <f>Calculations!E17</f>
         <v>2489200.5501423785</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101009A9DAB439B36DB4795F39C4E722C7BC4" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="44674c89fa9bc5e97a878a6680c46188">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="79748b23-d81a-423e-9112-21109dc864e6" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="447839a363ea5a12024b5bf1ab53ed90" ns2:_="">
+    <xsd:import namespace="79748b23-d81a-423e-9112-21109dc864e6"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="79748b23-d81a-423e-9112-21109dc864e6" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="11" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{069EC1CE-ACBC-4818-80F6-C59E6D5B6243}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{760667F4-47D9-4BFE-BCEA-A1FBB290E7CA}"/>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A3EBD543-73CF-4F31-8523-903D5BD0D909}"/>
 </file>